--- a/artfynd/A 58108-2024 artfynd.xlsx
+++ b/artfynd/A 58108-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,156 +957,6 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kärlväxtinventering Värmlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>16959176</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Berga, 500 m SÖ om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>363064.4165592435</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6636714.290937263</v>
-      </c>
-      <c r="S4" t="n">
-        <v>63</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Gunnarskog</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>S-Arv-0685</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2014-03-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2014-03-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>390 bladrosetter med 60 blomstänglar, rikligast vid 0673-7920 (RT 90), mindre grupper vid 0731-7942 i norr och 0651-7840 i väst</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre granskog med inslag av tallar, bitvis olikåldrigt</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
